--- a/Plotting/result_data_long_sensitivity.xlsx
+++ b/Plotting/result_data_long_sensitivity.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S126"/>
+  <dimension ref="A1:Y126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,25 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>EmissionLimit Brownfield</t>
-        </is>
-      </c>
+      <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EmissionLimit Brownfield</t>
+        </is>
+      </c>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="n"/>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -511,32 +517,46 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>TightEmission</t>
+          <t>noCO2electrolysis</t>
         </is>
       </c>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>MPWemission</t>
+          <t>TightEmission</t>
         </is>
       </c>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>OptBIO</t>
+          <t>MPWemission</t>
         </is>
       </c>
       <c r="O2" s="1" t="n"/>
       <c r="P2" s="1" t="n"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>TightEmission</t>
+          <t>OptBIO</t>
         </is>
       </c>
       <c r="R2" s="1" t="n"/>
       <c r="S2" s="1" t="n"/>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>noCO2electrolysis</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="n"/>
+      <c r="V2" s="1" t="n"/>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>TightEmission</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="n"/>
+      <c r="Y2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -634,6 +654,36 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="V3" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="W3" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -671,50 +721,80 @@
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Greenfield\OptBIO\20250530080651_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Greenfield\noCO2electrolysis\20250621051159_2030_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Greenfield\noCO2electrolysis\20250616154548_2040_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Greenfield\noCO2electrolysis\20250617112044_2050_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\MPWemission\20250604112817_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\MPWemission\20250604171113_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\MPWemission\20250605123112_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\OptBIO\20250525000900_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\OptBIO\20250525083318_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\OptBIO\20250531061128_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\noCO2electrolysis\20250620103829_2030_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\noCO2electrolysis\20250620144654_2040_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\noCO2electrolysis\20250620221757_2050_minC_DD10-1\optimization_results.h5</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\TightEmission\20250422114955_2030_tight_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\TightEmission\20250423094033_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionLimit Brownfield\TightEmission\20250423205830_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
@@ -744,34 +824,52 @@
       <c r="G6" t="n">
         <v>2321130066.491877</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="H6" t="n">
+        <v>4588025596.655902</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4641450369.996336</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3858339179.486997</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
         <v>5212378855.368991</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>4178210203.862845</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>3705197372.150028</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>4265874632.245741</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>3245775358.565355</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>1928392205.834014</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
+        <v>4540479208.314872</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4246761549.685172</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3748617381.521478</v>
+      </c>
+      <c r="W6" t="n">
         <v>4559346150.316367</v>
       </c>
-      <c r="R6" t="n">
+      <c r="X6" t="n">
         <v>3885941798.706064</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>3076760867.071573</v>
       </c>
     </row>
@@ -791,24 +889,34 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>394182578.6361811</v>
-      </c>
-      <c r="M7" t="n">
-        <v>732971699.1191738</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>393669027.0485265</v>
+        <v>394182578.6361811</v>
       </c>
       <c r="P7" t="n">
-        <v>661317569.6044121</v>
+        <v>732971699.1191738</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
+        <v>393669027.0485265</v>
+      </c>
+      <c r="S7" t="n">
+        <v>661317569.6044121</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>402112589.0050762</v>
+      </c>
+      <c r="V7" t="n">
+        <v>621607254.1023872</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
         <v>416292610.1242716</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>742345678.5369771</v>
       </c>
     </row>
@@ -827,31 +935,43 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>5212378855.368991</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>4572392782.499026</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>4438169071.269202</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>4265874632.245741</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>3639444385.613881</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>2589709775.438426</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
+        <v>4540479208.314872</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4648874138.690248</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4370224635.623865</v>
+      </c>
+      <c r="W8" t="n">
         <v>4559346150.316367</v>
       </c>
-      <c r="R8" t="n">
+      <c r="X8" t="n">
         <v>4302234408.830336</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Y8" t="n">
         <v>3819106545.60855</v>
       </c>
     </row>
@@ -879,22 +999,36 @@
       <c r="G9" t="n">
         <v>69633901994.75632</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>137640767899.6771</v>
+      </c>
+      <c r="I9" t="n">
+        <v>139243511099.8901</v>
+      </c>
+      <c r="J9" t="n">
+        <v>115750175384.6099</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>138287581305.0104</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>101013597662.4952</v>
+        <v>138287581305.0104</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
+        <v>101013597662.4952</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>131574653936.2391</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
         <v>122643944946.3098</v>
       </c>
     </row>
@@ -922,34 +1056,52 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="H10" t="n">
+        <v>540262.2929086428</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-29893.71281631262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>4195963.170609171</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>2086050.525512025</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>595460.2652924323</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>-32737.41303689824</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>524217.695470484</v>
+      </c>
+      <c r="U10" t="n">
+        <v>74030.62155935279</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>391902.9116249894</v>
       </c>
-      <c r="R10" t="n">
+      <c r="X10" t="n">
         <v>261268.6077499937</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="n">
         <v>4.190951585769653e-09</v>
       </c>
     </row>
@@ -977,34 +1129,52 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="H11" t="n">
+        <v>236.7734928783892</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1330.13857021508</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2160.395782581868</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>5.692399696527491</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>20.9957162706234</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>147.862735218242</v>
+      </c>
+      <c r="U11" t="n">
+        <v>622.5920496790684</v>
+      </c>
+      <c r="V11" t="n">
+        <v>465.8500374373652</v>
+      </c>
+      <c r="W11" t="n">
         <v>192.9097936337152</v>
       </c>
-      <c r="R11" t="n">
+      <c r="X11" t="n">
         <v>75.36402835536384</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Y11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1032,20 +1202,20 @@
       <c r="G12" t="n">
         <v>27.92410714285806</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="H12" t="n">
+        <v>29.34197701810812</v>
+      </c>
+      <c r="I12" t="n">
+        <v>29.54749257583014</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27.92410714284885</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>28.25175000000016</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>28.25175</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1062,6 +1232,24 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="n">
+        <v>28.25175000000005</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>28.25175</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1087,34 +1275,52 @@
       <c r="G13" t="n">
         <v>294.4170274170243</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="H13" t="n">
+        <v>65.28520926135005</v>
+      </c>
+      <c r="I13" t="n">
+        <v>91.73726819717741</v>
+      </c>
+      <c r="J13" t="n">
+        <v>124.2374499678485</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>293.3313131313654</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>293.3313131313126</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>64.27389941322461</v>
+      </c>
+      <c r="U13" t="n">
+        <v>91.24395511580245</v>
+      </c>
+      <c r="V13" t="n">
+        <v>56.79939450103026</v>
+      </c>
+      <c r="W13" t="n">
         <v>97.48130132670009</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>20.21234377128614</v>
       </c>
     </row>
@@ -1142,34 +1348,52 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="H14" t="n">
+        <v>128.054056069395</v>
+      </c>
+      <c r="I14" t="n">
+        <v>63.74787912007459</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>355.9465217391304</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>11.09031652173217</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>367.0368382608737</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>124.4386702139944</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5.17041719806253</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>122.1120081478671</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1197,34 +1421,52 @@
       <c r="G15" t="n">
         <v>34.81832506122186</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="J15" t="n">
+        <v>167.0555243736671</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>22.32469570638175</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>34.21735276344447</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>75.96386450450339</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>84.78000000000003</v>
+      </c>
+      <c r="V15" t="n">
+        <v>22.58635020330154</v>
+      </c>
+      <c r="W15" t="n">
         <v>30.85490464660982</v>
       </c>
-      <c r="R15" t="n">
+      <c r="X15" t="n">
         <v>98.69742744171411</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Y15" t="n">
         <v>66.40455921645506</v>
       </c>
     </row>
@@ -1252,18 +1494,18 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -1280,6 +1522,24 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1307,7 +1567,9 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1319,6 +1581,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1344,7 +1612,9 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1356,6 +1626,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1381,18 +1657,18 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -1409,6 +1685,24 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,18 +1730,18 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -1464,6 +1758,24 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1491,34 +1803,52 @@
       <c r="G21" t="n">
         <v>731.2995786559892</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="H21" t="n">
+        <v>696.4368753986289</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>744.2782040874093</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>744.2782040872602</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>751.7964890471458</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>739.7405494940336</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1546,18 +1876,18 @@
       <c r="G22" t="n">
         <v>803.5714285714286</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>813</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
+      <c r="H22" t="n">
+        <v>844.3734393700178</v>
+      </c>
+      <c r="I22" t="n">
+        <v>850.2875561389969</v>
+      </c>
+      <c r="J22" t="n">
+        <v>803.5714285714286</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>813</v>
       </c>
@@ -1576,6 +1906,24 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="n">
+        <v>813</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>813</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1601,18 +1949,18 @@
       <c r="G23" t="n">
         <v>803.5714285714286</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
+      <c r="H23" t="n">
+        <v>844.3734393700178</v>
+      </c>
+      <c r="I23" t="n">
+        <v>850.2875561389969</v>
+      </c>
+      <c r="J23" t="n">
+        <v>803.5714285714286</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -1629,6 +1977,24 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1656,34 +2022,52 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
+      <c r="H24" t="n">
+        <v>338</v>
+      </c>
+      <c r="I24" t="n">
+        <v>381</v>
+      </c>
+      <c r="J24" t="n">
+        <v>395.4587459370923</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
         <v>172.4261655881301</v>
       </c>
-      <c r="L24" t="n">
+      <c r="O24" t="n">
         <v>18.38785578319889</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>172.4261655881867</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>338</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
         <v>338.000000000002</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1711,34 +2095,52 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1023629699666549</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3130802599925144</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.8782033640659485</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.03530198910460498</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1766,34 +2168,52 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
+      <c r="H26" t="n">
+        <v>496.86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>560.0700000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>664.6341463414392</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
         <v>253.4664634145097</v>
       </c>
-      <c r="L26" t="n">
+      <c r="O26" t="n">
         <v>27.03014800130236</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>253.4664634146344</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>496.86</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>46.28089258433792</v>
+      </c>
+      <c r="W26" t="n">
         <v>496.8600000000021</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1821,18 +2241,18 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -1849,6 +2269,24 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>56.23437738072651</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1876,7 +2314,9 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1888,6 +2328,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1913,18 +2359,18 @@
       <c r="G29" t="n">
         <v>157</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>157</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
+      <c r="H29" t="n">
+        <v>64.06277066356205</v>
+      </c>
+      <c r="I29" t="n">
+        <v>39.92670547147824</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>157</v>
       </c>
@@ -1935,12 +2381,30 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
+        <v>157</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>64.06277066356245</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>64.06277066356211</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1968,18 +2432,18 @@
       <c r="G30" t="n">
         <v>218</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
+      <c r="H30" t="n">
         <v>218</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="n">
+        <v>218</v>
+      </c>
+      <c r="J30" t="n">
+        <v>218</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>218</v>
       </c>
@@ -1998,6 +2462,24 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="n">
+        <v>218</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>218</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2023,18 +2505,18 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -2051,6 +2533,24 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2078,7 +2578,9 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2090,6 +2592,12 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2115,7 +2623,9 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2127,6 +2637,12 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2152,34 +2668,52 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
+      <c r="H34" t="n">
+        <v>7907.625542418352</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11258.0544670957</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
         <v>3358.080000000625</v>
       </c>
-      <c r="L34" t="n">
+      <c r="O34" t="n">
         <v>5389.579798402184</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3656.881691911162</v>
       </c>
-      <c r="O34" t="n">
+      <c r="R34" t="n">
         <v>5433.115081792532</v>
       </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4209.975931226042</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4906.577668774064</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
         <v>4513.772281624878</v>
       </c>
-      <c r="R34" t="n">
+      <c r="X34" t="n">
         <v>4602.781318375011</v>
       </c>
-      <c r="S34" t="n">
+      <c r="Y34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2207,20 +2741,20 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
+      <c r="H35" t="n">
+        <v>1219.597246378784</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6414</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
         <v>1470.120398232947</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6414</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1432.828894956167</v>
       </c>
       <c r="O35" t="n">
         <v>6414</v>
@@ -2229,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1639.567763763904</v>
+        <v>1432.828894956167</v>
       </c>
       <c r="R35" t="n">
         <v>6414</v>
@@ -2237,6 +2771,24 @@
       <c r="S35" t="n">
         <v>0</v>
       </c>
+      <c r="T35" t="n">
+        <v>1662.788302475078</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6414</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1639.567763763904</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6414</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2262,34 +2814,52 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5221.209322686234</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>1618.796390936915</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>117.8412708295277</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>150.0338403346369</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
         <v>2135.750681559551</v>
       </c>
-      <c r="R36" t="n">
+      <c r="X36" t="n">
         <v>7669.396390915253</v>
       </c>
-      <c r="S36" t="n">
+      <c r="Y36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,34 +2887,52 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>1133.955909677429</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>477.4933451386743</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>81.27857645794155</v>
+      </c>
+      <c r="W37" t="n">
         <v>-1.30420139502345e-10</v>
       </c>
-      <c r="R37" t="n">
+      <c r="X37" t="n">
         <v>5336.698862648049</v>
       </c>
-      <c r="S37" t="n">
+      <c r="Y37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2372,34 +2960,52 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="H38" t="n">
+        <v>128.9619661763162</v>
+      </c>
+      <c r="I38" t="n">
+        <v>32492.5375231674</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>494.7538811396987</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
         <v>694.8902024726615</v>
       </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>195.077159682388</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3234.356231297521</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
         <v>270.0426815626308</v>
       </c>
-      <c r="R38" t="n">
+      <c r="X38" t="n">
         <v>8471.55242708012</v>
       </c>
-      <c r="S38" t="n">
+      <c r="Y38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2427,34 +3033,52 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>6808.828146592633</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
         <v>7147.624402790782</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>78.87104875403671</v>
+      </c>
+      <c r="W39" t="n">
         <v>-4.145765562074552e-10</v>
       </c>
-      <c r="R39" t="n">
+      <c r="X39" t="n">
         <v>498.5668092198713</v>
       </c>
-      <c r="S39" t="n">
+      <c r="Y39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2482,34 +3106,52 @@
       <c r="G40" t="n">
         <v>136.75302120867</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
+      <c r="H40" t="n">
+        <v>130.2336956995436</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
         <v>139.1800241643082</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>0.1963241017880827</v>
       </c>
-      <c r="N40" t="n">
+      <c r="Q40" t="n">
         <v>139.1800241643176</v>
       </c>
-      <c r="O40" t="n">
+      <c r="R40" t="n">
         <v>7.509193214636699</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>140.5859434518163</v>
+      </c>
+      <c r="U40" t="n">
+        <v>18.3055590176057</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
         <v>138.3314827553843</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2537,34 +3179,52 @@
       <c r="G41" t="n">
         <v>738.299578656593</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="n">
+      <c r="H41" t="n">
+        <v>803.0229133067216</v>
+      </c>
+      <c r="I41" t="n">
+        <v>70.7478791200746</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
         <v>1066.928204086812</v>
       </c>
-      <c r="L41" t="n">
+      <c r="O41" t="n">
         <v>25.85494422550943</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1066.928204087278</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>0.6708666579442024</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="T41" t="n">
+        <v>853.603541563921</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>845.1149737344946</v>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2592,18 +3252,18 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -2620,6 +3280,24 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2647,18 +3325,18 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>0</v>
       </c>
@@ -2675,6 +3353,24 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>56.23437738072651</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2702,18 +3398,18 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -2730,6 +3426,24 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2757,34 +3471,52 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="n">
+      <c r="H45" t="n">
+        <v>96.2616902684085</v>
+      </c>
+      <c r="I45" t="n">
+        <v>62.37464952854114</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.435396836971421</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
         <v>105.896886028623</v>
       </c>
-      <c r="L45" t="n">
+      <c r="O45" t="n">
         <v>45.9381316150001</v>
       </c>
-      <c r="M45" t="n">
+      <c r="P45" t="n">
         <v>105.8968860250001</v>
       </c>
-      <c r="N45" t="n">
+      <c r="Q45" t="n">
         <v>105.8968860251569</v>
       </c>
-      <c r="O45" t="n">
+      <c r="R45" t="n">
         <v>108.4606122400019</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>107.4110610977328</v>
+      </c>
+      <c r="U45" t="n">
         <v>114</v>
       </c>
-      <c r="R45" t="n">
+      <c r="V45" t="n">
+        <v>83.18529132198913</v>
+      </c>
+      <c r="W45" t="n">
         <v>114</v>
       </c>
-      <c r="S45" t="n">
+      <c r="X45" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y45" t="n">
         <v>148</v>
       </c>
     </row>
@@ -2812,34 +3544,52 @@
       <c r="G46" t="n">
         <v>34.81832506362986</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>56.54204846982621</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>75.96386450450339</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
         <v>1.4210854715202e-14</v>
       </c>
-      <c r="S46" t="n">
+      <c r="Y46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2867,18 +3617,18 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>0</v>
       </c>
@@ -2895,6 +3645,24 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2922,18 +3690,18 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>0</v>
       </c>
@@ -2950,6 +3718,24 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2977,18 +3763,18 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -3005,6 +3791,24 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3032,18 +3836,18 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
         <v>0</v>
       </c>
@@ -3060,6 +3864,24 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3087,18 +3909,18 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -3115,6 +3937,24 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3142,34 +3982,52 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="n">
+      <c r="H52" t="n">
+        <v>338</v>
+      </c>
+      <c r="I52" t="n">
+        <v>381</v>
+      </c>
+      <c r="J52" t="n">
+        <v>395.4587460988701</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
         <v>172.4261655902637</v>
       </c>
-      <c r="L52" t="n">
+      <c r="O52" t="n">
         <v>18.38785578319889</v>
       </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
         <v>172.4261655882828</v>
       </c>
-      <c r="O52" t="n">
+      <c r="R52" t="n">
         <v>172.4261655881867</v>
       </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>338</v>
+      </c>
+      <c r="U52" t="n">
+        <v>338</v>
+      </c>
+      <c r="V52" t="n">
+        <v>338</v>
+      </c>
+      <c r="W52" t="n">
         <v>338.000000000002</v>
       </c>
-      <c r="R52" t="n">
+      <c r="X52" t="n">
         <v>338.000000000002</v>
       </c>
-      <c r="S52" t="n">
+      <c r="Y52" t="n">
         <v>338</v>
       </c>
     </row>
@@ -3197,18 +4055,18 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>0</v>
       </c>
@@ -3225,6 +4083,24 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3252,18 +4128,18 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>0</v>
       </c>
@@ -3280,6 +4156,24 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3307,18 +4201,18 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>0</v>
       </c>
@@ -3335,6 +4229,24 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3362,18 +4274,18 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>0</v>
       </c>
@@ -3390,6 +4302,24 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3417,18 +4347,18 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>0</v>
       </c>
@@ -3445,6 +4375,24 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3472,18 +4420,18 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>0</v>
       </c>
@@ -3500,6 +4448,24 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3527,18 +4493,18 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>0</v>
       </c>
@@ -3555,6 +4521,24 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3582,18 +4566,18 @@
       <c r="G60" t="n">
         <v>2259.261963825666</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
+      <c r="H60" t="n">
         <v>750</v>
       </c>
-      <c r="L60" t="n">
+      <c r="I60" t="n">
         <v>2000</v>
       </c>
-      <c r="M60" t="n">
-        <v>2500.000000000001</v>
-      </c>
+      <c r="J60" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
         <v>750</v>
       </c>
@@ -3601,17 +4585,35 @@
         <v>2000</v>
       </c>
       <c r="P60" t="n">
-        <v>2500</v>
+        <v>2500.000000000001</v>
       </c>
       <c r="Q60" t="n">
-        <v>750.000000000004</v>
+        <v>750</v>
       </c>
       <c r="R60" t="n">
-        <v>2000.000000000002</v>
+        <v>2000</v>
       </c>
       <c r="S60" t="n">
         <v>2500</v>
       </c>
+      <c r="T60" t="n">
+        <v>750</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2441.693789547481</v>
+      </c>
+      <c r="W60" t="n">
+        <v>750.000000000004</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2000.000000000002</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -3637,18 +4639,18 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
         <v>0</v>
       </c>
@@ -3665,6 +4667,24 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3692,18 +4712,18 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
         <v>0</v>
       </c>
@@ -3720,6 +4740,24 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3747,18 +4785,18 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
         <v>0</v>
       </c>
@@ -3775,6 +4813,24 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3802,18 +4858,18 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
         <v>0</v>
       </c>
@@ -3830,6 +4886,24 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3857,18 +4931,18 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
         <v>0</v>
       </c>
@@ -3885,6 +4959,24 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3912,18 +5004,18 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
         <v>0</v>
       </c>
@@ -3940,6 +5032,24 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3967,18 +5077,18 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
         <v>0</v>
       </c>
@@ -3995,6 +5105,24 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4022,18 +5150,18 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>0</v>
       </c>
@@ -4050,6 +5178,24 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4077,34 +5223,52 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
+      <c r="H69" t="n">
+        <v>38.59407933917745</v>
+      </c>
+      <c r="I69" t="n">
+        <v>216.812586945058</v>
+      </c>
+      <c r="J69" t="n">
+        <v>352.1445126154395</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>0.927861150533981</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
         <v>3.422301752111614</v>
       </c>
-      <c r="P69" t="n">
+      <c r="S69" t="n">
         <v>0.6844603504223223</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="T69" t="n">
+        <v>24.10162584057344</v>
+      </c>
+      <c r="U69" t="n">
+        <v>125.5841299382616</v>
+      </c>
+      <c r="V69" t="n">
+        <v>201.5176860405521</v>
+      </c>
+      <c r="W69" t="n">
         <v>31.44429636269888</v>
       </c>
-      <c r="R69" t="n">
+      <c r="X69" t="n">
         <v>43.72863298421989</v>
       </c>
-      <c r="S69" t="n">
+      <c r="Y69" t="n">
         <v>43.72863298421987</v>
       </c>
     </row>
@@ -4132,18 +5296,18 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
         <v>0</v>
       </c>
@@ -4160,6 +5324,24 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4187,18 +5369,18 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>0</v>
       </c>
@@ -4215,6 +5397,24 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4242,34 +5442,52 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="n">
+      <c r="H72" t="n">
+        <v>803.0229133067216</v>
+      </c>
+      <c r="I72" t="n">
+        <v>70.7478791200746</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
         <v>1066.928204089392</v>
       </c>
-      <c r="L72" t="n">
+      <c r="O72" t="n">
         <v>1092.783148312321</v>
       </c>
-      <c r="M72" t="n">
+      <c r="P72" t="n">
         <v>162.4757600703234</v>
       </c>
-      <c r="N72" t="n">
+      <c r="Q72" t="n">
         <v>1066.928204087566</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>853.603541563921</v>
+      </c>
+      <c r="U72" t="n">
+        <v>827.9607938514199</v>
+      </c>
+      <c r="V72" t="n">
+        <v>758.7964890471458</v>
+      </c>
+      <c r="W72" t="n">
         <v>845.1149737344946</v>
       </c>
-      <c r="R72" t="n">
+      <c r="X72" t="n">
         <v>746.7405494940336</v>
       </c>
-      <c r="S72" t="n">
+      <c r="Y72" t="n">
         <v>746.7405494940336</v>
       </c>
     </row>
@@ -4297,18 +5515,18 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
         <v>0</v>
       </c>
@@ -4325,6 +5543,24 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4352,34 +5588,52 @@
       <c r="G74" t="n">
         <v>738.299578657107</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
         <v>751.2782040874093</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
         <v>1066.928204087267</v>
       </c>
-      <c r="P74" t="n">
+      <c r="S74" t="n">
         <v>1067.599070745222</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4407,18 +5661,18 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
         <v>0</v>
       </c>
@@ -4435,6 +5689,24 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4462,18 +5734,18 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
         <v>0</v>
       </c>
@@ -4490,6 +5762,24 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4517,18 +5807,18 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
         <v>0</v>
       </c>
@@ -4545,6 +5835,24 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4572,18 +5880,18 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
         <v>0</v>
       </c>
@@ -4600,6 +5908,24 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4627,18 +5953,18 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
         <v>0</v>
       </c>
@@ -4655,6 +5981,24 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4682,18 +6026,18 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
         <v>0</v>
       </c>
@@ -4710,6 +6054,24 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4737,18 +6099,18 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
         <v>0</v>
       </c>
@@ -4765,6 +6127,24 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4792,18 +6172,18 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
         <v>0</v>
       </c>
@@ -4820,6 +6200,24 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4847,34 +6245,52 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
         <v>6.394884621840902e-13</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
       <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
         <v>1.4210854715202e-14</v>
       </c>
-      <c r="R83" t="n">
+      <c r="X83" t="n">
         <v>2.842170943040401e-14</v>
       </c>
-      <c r="S83" t="n">
+      <c r="Y83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4902,18 +6318,18 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
         <v>0</v>
       </c>
@@ -4930,6 +6346,24 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4957,18 +6391,18 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
         <v>0</v>
       </c>
@@ -4985,6 +6419,24 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5012,18 +6464,18 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
         <v>0</v>
       </c>
@@ -5040,6 +6492,24 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5067,34 +6537,52 @@
       <c r="G87" t="n">
         <v>34.26287946433737</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="n">
+      <c r="H87" t="n">
+        <v>71.28185624009866</v>
+      </c>
+      <c r="I87" t="n">
+        <v>234.4454203525905</v>
+      </c>
+      <c r="J87" t="n">
+        <v>356.1618513485121</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="n">
         <v>34.66489725022941</v>
       </c>
-      <c r="L87" t="n">
+      <c r="O87" t="n">
         <v>34.6648972500002</v>
       </c>
-      <c r="M87" t="n">
+      <c r="P87" t="n">
         <v>35.5130648047828</v>
       </c>
-      <c r="N87" t="n">
+      <c r="Q87" t="n">
         <v>34.66489725003473</v>
       </c>
-      <c r="O87" t="n">
+      <c r="R87" t="n">
         <v>37.7932589743229</v>
       </c>
-      <c r="P87" t="n">
+      <c r="S87" t="n">
         <v>35.29056959486458</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="T87" t="n">
+        <v>56.69644479751813</v>
+      </c>
+      <c r="U87" t="n">
+        <v>149.4626601996993</v>
+      </c>
+      <c r="V87" t="n">
+        <v>218.8743157778667</v>
+      </c>
+      <c r="W87" t="n">
         <v>63.40845650179223</v>
       </c>
-      <c r="R87" t="n">
+      <c r="X87" t="n">
         <v>74.63769672637277</v>
       </c>
-      <c r="S87" t="n">
+      <c r="Y87" t="n">
         <v>74.63769672637278</v>
       </c>
     </row>
@@ -5122,18 +6610,18 @@
       <c r="G88" t="n">
         <v>157</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>157</v>
-      </c>
-      <c r="L88" t="n">
-        <v>157</v>
-      </c>
-      <c r="M88" t="n">
-        <v>157.0000000000212</v>
-      </c>
+      <c r="H88" t="n">
+        <v>64.0627706636562</v>
+      </c>
+      <c r="I88" t="n">
+        <v>39.92670547202766</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
         <v>157</v>
       </c>
@@ -5141,15 +6629,33 @@
         <v>157</v>
       </c>
       <c r="P88" t="n">
+        <v>157.0000000000212</v>
+      </c>
+      <c r="Q88" t="n">
         <v>157</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="R88" t="n">
+        <v>157</v>
+      </c>
+      <c r="S88" t="n">
+        <v>157</v>
+      </c>
+      <c r="T88" t="n">
+        <v>64.06277066362065</v>
+      </c>
+      <c r="U88" t="n">
+        <v>64.06277066418828</v>
+      </c>
+      <c r="V88" t="n">
+        <v>64.06277066356246</v>
+      </c>
+      <c r="W88" t="n">
         <v>64.0627706654365</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5177,18 +6683,18 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
         <v>0</v>
       </c>
@@ -5205,6 +6711,24 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5232,18 +6756,18 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
         <v>0</v>
       </c>
@@ -5260,6 +6784,24 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5287,18 +6829,18 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
         <v>0</v>
       </c>
@@ -5315,6 +6857,24 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5342,18 +6902,18 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
         <v>0</v>
       </c>
@@ -5370,6 +6930,24 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5397,18 +6975,18 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
         <v>0</v>
       </c>
@@ -5422,9 +7000,27 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
         <v>83.07456133439007</v>
       </c>
-      <c r="S93" t="n">
+      <c r="Y93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5452,18 +7048,18 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
         <v>0</v>
       </c>
@@ -5480,6 +7076,24 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5507,18 +7121,18 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
         <v>0</v>
       </c>
@@ -5535,6 +7149,24 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5562,18 +7194,18 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
         <v>0</v>
       </c>
@@ -5590,6 +7222,24 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5617,18 +7267,18 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
         <v>0</v>
       </c>
@@ -5645,6 +7295,24 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5672,24 +7340,30 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="n">
-        <v>129.2870380582895</v>
-      </c>
-      <c r="M98" t="n">
-        <v>32.22911136728798</v>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
-        <v>103.3331598099383</v>
+        <v>129.2870380582895</v>
       </c>
       <c r="P98" t="n">
-        <v>38.58608326683546</v>
+        <v>32.22911136728798</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
+        <v>103.3331598099383</v>
+      </c>
+      <c r="S98" t="n">
+        <v>38.58608326683546</v>
+      </c>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="n">
         <v>111.6469841152122</v>
       </c>
-      <c r="S98" t="n">
+      <c r="Y98" t="n">
         <v>39.57950136806033</v>
       </c>
     </row>
@@ -5714,15 +7388,15 @@
         <v>0</v>
       </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>121.6201311153382</v>
+      </c>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>0</v>
@@ -5735,6 +7409,20 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5753,9 +7441,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
@@ -5768,6 +7454,16 @@
       </c>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -5784,9 +7480,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
@@ -5799,6 +7493,16 @@
       </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -5815,15 +7519,9 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="n">
-        <v>813</v>
-      </c>
-      <c r="L102" t="n">
-        <v>813</v>
-      </c>
-      <c r="M102" t="n">
-        <v>813</v>
-      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
         <v>813</v>
       </c>
@@ -5840,6 +7538,24 @@
         <v>813</v>
       </c>
       <c r="S102" t="n">
+        <v>813</v>
+      </c>
+      <c r="T102" t="n">
+        <v>813</v>
+      </c>
+      <c r="U102" t="n">
+        <v>813</v>
+      </c>
+      <c r="V102" t="n">
+        <v>813</v>
+      </c>
+      <c r="W102" t="n">
+        <v>813</v>
+      </c>
+      <c r="X102" t="n">
+        <v>813</v>
+      </c>
+      <c r="Y102" t="n">
         <v>813</v>
       </c>
     </row>
@@ -5858,9 +7574,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
@@ -5873,6 +7587,16 @@
       </c>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -5889,9 +7613,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
@@ -5900,10 +7622,20 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="n">
-        <v>-1.343301136820301e-13</v>
+        <v>0</v>
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="n">
+        <v>-1.343301136820301e-13</v>
+      </c>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -5920,9 +7652,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
@@ -5935,6 +7665,16 @@
       </c>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -5952,24 +7692,34 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="n">
-        <v>28.25175000000016</v>
-      </c>
-      <c r="M106" t="n">
-        <v>28.25175000000016</v>
-      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>28.25175</v>
+        <v>28.25175000000016</v>
       </c>
       <c r="P106" t="n">
-        <v>28.25175</v>
+        <v>28.25175000000016</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="n">
         <v>28.25175</v>
       </c>
       <c r="S106" t="n">
+        <v>28.25175</v>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="n">
+        <v>28.25175000000005</v>
+      </c>
+      <c r="V106" t="n">
+        <v>28.25175000000005</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="n">
+        <v>28.25175</v>
+      </c>
+      <c r="Y106" t="n">
         <v>28.25175</v>
       </c>
     </row>
@@ -5989,24 +7739,34 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="n">
-        <v>293.3313131313654</v>
-      </c>
-      <c r="M107" t="n">
-        <v>293.3313131313654</v>
-      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
-        <v>293.3313131313126</v>
+        <v>293.3313131313654</v>
       </c>
       <c r="P107" t="n">
-        <v>293.3313131313126</v>
+        <v>293.3313131313654</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
+        <v>293.3313131313126</v>
+      </c>
+      <c r="S107" t="n">
+        <v>293.3313131313126</v>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="n">
+        <v>64.27389941322461</v>
+      </c>
+      <c r="V107" t="n">
+        <v>155.5178545290271</v>
+      </c>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="n">
         <v>97.48130132670009</v>
       </c>
-      <c r="S107" t="n">
+      <c r="Y107" t="n">
         <v>97.48130132670009</v>
       </c>
     </row>
@@ -6026,24 +7786,34 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="n">
-        <v>355.9465217391304</v>
-      </c>
-      <c r="M108" t="n">
-        <v>367.0368382608626</v>
-      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
-        <v>367.0368382608737</v>
+        <v>355.9465217391304</v>
       </c>
       <c r="P108" t="n">
-        <v>367.0368382608737</v>
+        <v>367.0368382608626</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
+        <v>367.0368382608737</v>
+      </c>
+      <c r="S108" t="n">
+        <v>367.0368382608737</v>
+      </c>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="n">
+        <v>124.4386702139944</v>
+      </c>
+      <c r="V108" t="n">
+        <v>129.6090874120569</v>
+      </c>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="n">
         <v>122.1120081478671</v>
       </c>
-      <c r="S108" t="n">
+      <c r="Y108" t="n">
         <v>122.1120081478671</v>
       </c>
     </row>
@@ -6063,24 +7833,34 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="n">
-        <v>744.2782040874093</v>
-      </c>
-      <c r="M109" t="n">
-        <v>744.2782040874093</v>
-      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
-        <v>744.2782040872602</v>
+        <v>744.2782040874093</v>
       </c>
       <c r="P109" t="n">
-        <v>744.2782040872602</v>
+        <v>744.2782040874093</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
+        <v>744.2782040872602</v>
+      </c>
+      <c r="S109" t="n">
+        <v>744.2782040872602</v>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="n">
+        <v>751.7964890471458</v>
+      </c>
+      <c r="V109" t="n">
+        <v>751.7964890471458</v>
+      </c>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="n">
         <v>739.7405494940336</v>
       </c>
-      <c r="S109" t="n">
+      <c r="Y109" t="n">
         <v>739.7405494940336</v>
       </c>
     </row>
@@ -6100,12 +7880,8 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="n">
-        <v>813</v>
-      </c>
-      <c r="M110" t="n">
-        <v>813</v>
-      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
         <v>813</v>
@@ -6118,6 +7894,20 @@
         <v>813</v>
       </c>
       <c r="S110" t="n">
+        <v>813</v>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v>813</v>
+      </c>
+      <c r="V110" t="n">
+        <v>813</v>
+      </c>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="n">
+        <v>813</v>
+      </c>
+      <c r="Y110" t="n">
         <v>813</v>
       </c>
     </row>
@@ -6137,24 +7927,34 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
-        <v>172.4261655881301</v>
-      </c>
-      <c r="M111" t="n">
-        <v>190.814021371329</v>
-      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>172.4261655881867</v>
+        <v>172.4261655881301</v>
       </c>
       <c r="P111" t="n">
-        <v>172.4261655881867</v>
+        <v>190.814021371329</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
+        <v>172.4261655881867</v>
+      </c>
+      <c r="S111" t="n">
+        <v>172.4261655881867</v>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="n">
+        <v>338</v>
+      </c>
+      <c r="V111" t="n">
+        <v>338</v>
+      </c>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="n">
         <v>338.000000000002</v>
       </c>
-      <c r="S111" t="n">
+      <c r="Y111" t="n">
         <v>338.000000000002</v>
       </c>
     </row>
@@ -6174,12 +7974,8 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
         <v>0</v>
@@ -6189,9 +7985,23 @@
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="n">
+        <v>0.08625872255370338</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0.2296659825736221</v>
+      </c>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="n">
         <v>0.286640155536481</v>
       </c>
-      <c r="S112" t="n">
+      <c r="Y112" t="n">
         <v>0.5364496303699052</v>
       </c>
     </row>
@@ -6211,24 +8021,34 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="n">
-        <v>253.4664634145097</v>
-      </c>
-      <c r="M113" t="n">
-        <v>280.496611415812</v>
-      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
-        <v>253.4664634146344</v>
+        <v>253.4664634145097</v>
       </c>
       <c r="P113" t="n">
-        <v>253.4664634146344</v>
+        <v>280.496611415812</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
+        <v>253.4664634146344</v>
+      </c>
+      <c r="S113" t="n">
+        <v>253.4664634146344</v>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="n">
+        <v>496.86</v>
+      </c>
+      <c r="V113" t="n">
+        <v>496.86</v>
+      </c>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="n">
         <v>496.8600000000021</v>
       </c>
-      <c r="S113" t="n">
+      <c r="Y113" t="n">
         <v>496.8600000000021</v>
       </c>
     </row>
@@ -6248,12 +8068,8 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
-        <v>157</v>
-      </c>
-      <c r="M114" t="n">
-        <v>157</v>
-      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
         <v>157</v>
@@ -6263,9 +8079,23 @@
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
+        <v>157</v>
+      </c>
+      <c r="S114" t="n">
+        <v>157</v>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="n">
+        <v>64.06277066356245</v>
+      </c>
+      <c r="V114" t="n">
+        <v>64.06277066356245</v>
+      </c>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="n">
         <v>64.06277066356211</v>
       </c>
-      <c r="S114" t="n">
+      <c r="Y114" t="n">
         <v>64.06277066356211</v>
       </c>
     </row>
@@ -6285,12 +8115,8 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
-        <v>218</v>
-      </c>
-      <c r="M115" t="n">
-        <v>218</v>
-      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
         <v>218</v>
@@ -6303,6 +8129,20 @@
         <v>218</v>
       </c>
       <c r="S115" t="n">
+        <v>218</v>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="n">
+        <v>218</v>
+      </c>
+      <c r="V115" t="n">
+        <v>218</v>
+      </c>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="n">
+        <v>218</v>
+      </c>
+      <c r="Y115" t="n">
         <v>218</v>
       </c>
     </row>
@@ -6322,24 +8162,34 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>3358.080000000625</v>
-      </c>
-      <c r="M116" t="n">
-        <v>8747.659798402809</v>
-      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="n">
-        <v>3656.881691911162</v>
+        <v>3358.080000000625</v>
       </c>
       <c r="P116" t="n">
-        <v>9089.996773703693</v>
+        <v>8747.659798402809</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="n">
+        <v>3656.881691911162</v>
+      </c>
+      <c r="S116" t="n">
+        <v>9089.996773703693</v>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="n">
+        <v>4209.975931226042</v>
+      </c>
+      <c r="V116" t="n">
+        <v>9116.553600000107</v>
+      </c>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="n">
         <v>4513.772281624878</v>
       </c>
-      <c r="S116" t="n">
+      <c r="Y116" t="n">
         <v>9116.55359999989</v>
       </c>
     </row>
@@ -6359,24 +8209,34 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="n">
-        <v>1470.120398232947</v>
-      </c>
-      <c r="M117" t="n">
-        <v>7884.120398232947</v>
-      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
-        <v>1432.828894956167</v>
+        <v>1470.120398232947</v>
       </c>
       <c r="P117" t="n">
-        <v>7846.828894956167</v>
+        <v>7884.120398232947</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
+        <v>1432.828894956167</v>
+      </c>
+      <c r="S117" t="n">
+        <v>7846.828894956167</v>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="n">
+        <v>1662.788302475078</v>
+      </c>
+      <c r="V117" t="n">
+        <v>8076.788302475078</v>
+      </c>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="n">
         <v>1639.567763763904</v>
       </c>
-      <c r="S117" t="n">
+      <c r="Y117" t="n">
         <v>8053.567763763904</v>
       </c>
     </row>
@@ -6396,24 +8256,34 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
-        <v>139.1800241643082</v>
-      </c>
-      <c r="M118" t="n">
-        <v>139.1800241643082</v>
-      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
-        <v>139.1800241643176</v>
+        <v>139.1800241643082</v>
       </c>
       <c r="P118" t="n">
-        <v>146.6892173789543</v>
+        <v>139.1800241643082</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
+        <v>139.1800241643176</v>
+      </c>
+      <c r="S118" t="n">
+        <v>146.6892173789543</v>
+      </c>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="n">
+        <v>140.5859434518163</v>
+      </c>
+      <c r="V118" t="n">
+        <v>158.891502469422</v>
+      </c>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="n">
         <v>138.3314827553843</v>
       </c>
-      <c r="S118" t="n">
+      <c r="Y118" t="n">
         <v>138.3314827553843</v>
       </c>
     </row>
@@ -6433,24 +8303,34 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>1066.928204086812</v>
-      </c>
-      <c r="M119" t="n">
-        <v>1092.783148312321</v>
-      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>1066.928204087278</v>
+        <v>1066.928204086812</v>
       </c>
       <c r="P119" t="n">
-        <v>1066.928204087278</v>
+        <v>1092.783148312321</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
+        <v>1066.928204087278</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1066.928204087278</v>
+      </c>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="n">
+        <v>853.603541563921</v>
+      </c>
+      <c r="V119" t="n">
+        <v>853.603541563921</v>
+      </c>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="n">
         <v>845.1149737344946</v>
       </c>
-      <c r="S119" t="n">
+      <c r="Y119" t="n">
         <v>845.1149737344946</v>
       </c>
     </row>
@@ -6471,17 +8351,25 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="n">
-        <v>22.32469570638175</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>22.32469570638175</v>
+      </c>
       <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="n">
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="n">
+        <v>84.78000000000003</v>
+      </c>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="n">
         <v>30.85490464660982</v>
       </c>
-      <c r="S120" t="n">
+      <c r="Y120" t="n">
         <v>129.5523320883239</v>
       </c>
     </row>
@@ -6502,17 +8390,23 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="n">
-        <v>129.2870380582895</v>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>103.3331598099383</v>
+        <v>129.2870380582895</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
+        <v>103.3331598099383</v>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="n">
         <v>111.6469841152122</v>
       </c>
     </row>
@@ -6533,19 +8427,25 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="n">
-        <v>1618.796390936915</v>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
+        <v>1618.796390936915</v>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="n">
         <v>117.8412708295277</v>
       </c>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="n">
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="n">
         <v>2135.750681559551</v>
       </c>
-      <c r="S122" t="n">
+      <c r="Y122" t="n">
         <v>9805.147072474803</v>
       </c>
     </row>
@@ -6566,17 +8466,23 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="n">
-        <v>1133.955909677429</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
-        <v>477.4933451386743</v>
+        <v>1133.955909677429</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
+        <v>477.4933451386743</v>
+      </c>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="n">
         <v>5336.698862648049</v>
       </c>
     </row>
@@ -6597,19 +8503,29 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="n">
-        <v>494.7538811396987</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
+        <v>494.7538811396987</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="n">
         <v>694.8902024726615</v>
       </c>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="n">
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="n">
+        <v>195.077159682388</v>
+      </c>
+      <c r="V124" t="n">
+        <v>3429.433390979909</v>
+      </c>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="n">
         <v>270.0426815626308</v>
       </c>
-      <c r="S124" t="n">
+      <c r="Y124" t="n">
         <v>8741.59510864275</v>
       </c>
     </row>
@@ -6630,17 +8546,23 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="n">
-        <v>6808.828146592633</v>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
-        <v>7147.624402790782</v>
+        <v>6808.828146592633</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
+        <v>7147.624402790782</v>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="n">
         <v>498.5668092198713</v>
       </c>
     </row>
@@ -6664,27 +8586,39 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="n">
         <v>20.9957162706234</v>
       </c>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="n">
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="n">
+        <v>147.862735218242</v>
+      </c>
+      <c r="V126" t="n">
+        <v>770.4547848973103</v>
+      </c>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="n">
         <v>192.9097936337152</v>
       </c>
-      <c r="S126" t="n">
+      <c r="Y126" t="n">
         <v>268.273821989079</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="T2:V2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B1:M1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="N1:Y1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
